--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573360461</v>
+        <v>46157.93114099564</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114099564</v>
+        <v>46157.93180839919</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93180839919</v>
+        <v>46157.93404762212</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404762212</v>
+        <v>46157.93722828928</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722828928</v>
+        <v>46158.28220704033</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220704033</v>
+        <v>46158.29697630413</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29697630413</v>
+        <v>46158.29820251111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820251111</v>
+        <v>46158.33391673646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391673646</v>
+        <v>46158.36861497677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/1. АвтоТехЦентр (ИП Петраш Г.М.)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861497677</v>
+        <v>46158.37292125543</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
